--- a/ig/DM-37/CodeSystem-TRE-R239-PublicPrisEnCharge.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R239-PublicPrisEnCharge.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>Etudiants</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Personnes atteintes de pathologies chroniques ou présentant une ALD</t>
   </si>
 </sst>
 </file>
@@ -585,7 +591,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -698,6 +704,18 @@
       </c>
       <c r="D9" s="2"/>
     </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
